--- a/astro-site/public/dl/catering-business-plan/catering-pricing-calculator.xlsx
+++ b/astro-site/public/dl/catering-business-plan/catering-pricing-calculator.xlsx
@@ -786,7 +786,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>A mandatory service charge is wages, not a tip (IRS Rev. Rul. 2012-18). Kit estimate.</t>
+          <t>Added on top of the price per guest. The part you pay out to staff is wages, not tips (IRS Rev. Rul. 2012-18), with payroll taxes; the part you keep is revenue. Kit estimate.</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CA: a mandatory service charge is taxable. NY: not taxable only if it is separately stated as a gratuity and all of it goes to the staff. TX: not taxable up to 20% if separately stated and distributed to qualified employees. Check your state.</t>
+          <t>CA: a mandatory service charge is taxable. NY: not taxable only if it is separately stated, identified as a gratuity and all of it goes to the staff. TX: not taxable up to 20% if separately stated, identified as a gratuity and paid to qualified employees (servers and bartenders, not chefs); over 20%, all of it is taxable. Check your state.</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PRICE PER GUEST (rounded up to the next 0.50)</t>
+          <t>PRICE PER GUEST before service charge and tax</t>
         </is>
       </c>
       <c r="B32" s="14">
@@ -952,7 +952,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Excl. service charge and sales tax.</t>
+          <t>Rounded up to the next 0.50. Excl. service charge and sales tax; staff wages are already inside it.</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PRICE PER GUEST (rounded up to the next 0.50)</t>
+          <t>PRICE PER GUEST before service charge and tax</t>
         </is>
       </c>
       <c r="B32" s="14">
@@ -2073,17 +2073,17 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="45" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>A mandatory service charge is not a tip: the IRS treats it as wages paid to the staff, with payroll taxes (Rev. Rul. 2012-18). A voluntary gratuity is the client's decision: this calculator keeps it out of the price and the total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
+          <t>A mandatory service charge is not a tip: the part you pay out to the staff is wages, with payroll taxes (IRS Rev. Rul. 2012-18), and the part you keep is revenue. A voluntary gratuity is the client's decision: this calculator keeps it out of the price and the total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="75" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Sales tax on catering: in many states it applies to the whole catering invoice (food, staff, rentals). Whether it also applies to the service charge depends on the state: in California a mandatory service charge is taxable; in New York it is not taxable only when it is separately stated as a gratuity and all of it goes to the staff; in Texas it is not taxable up to 20% if separately stated and distributed to qualified employees. Check your state's rules and set the switch.</t>
+          <t>Sales tax on catering: in many states it applies to the whole catering invoice (food, staff, rentals). Whether it also applies to the service charge depends on the state: in California a mandatory service charge is taxable; in New York it is not taxable only when it is separately stated, identified as a gratuity and all of it goes to the staff; in Texas it is not taxable up to 20% if separately stated, identified as a gratuity and paid to qualified employees (servers and bartenders, not chefs), and over 20% all of it is taxable. Check your state's rules and set the switch.</t>
         </is>
       </c>
     </row>
